--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>Prepared for CA</t>
+  </si>
+  <si>
+    <t>Went outside</t>
   </si>
 </sst>
 </file>
@@ -3034,26 +3037,50 @@
       </c>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="11"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="13" t="str">
+      <c r="A40" s="11">
+        <v>46274</v>
+      </c>
+      <c r="B40" s="12">
+        <v>340</v>
+      </c>
+      <c r="C40" s="12">
+        <v>20</v>
+      </c>
+      <c r="D40" s="12">
+        <v>50</v>
+      </c>
+      <c r="E40" s="12">
+        <v>120</v>
+      </c>
+      <c r="F40" s="12">
+        <v>250</v>
+      </c>
+      <c r="G40" s="12">
+        <v>5</v>
+      </c>
+      <c r="H40" s="12">
+        <v>140</v>
+      </c>
+      <c r="I40" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="13" t="str">
+        <v>920</v>
+      </c>
+      <c r="J40" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="15"/>
+        <v>520</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N40" s="15" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>Went outside</t>
+  </si>
+  <si>
+    <t>Had a Headache</t>
   </si>
 </sst>
 </file>
@@ -3053,21 +3056,21 @@
         <v>120</v>
       </c>
       <c r="F40" s="12">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G40" s="12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H40" s="12">
         <v>140</v>
       </c>
       <c r="I40" s="13">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>770</v>
       </c>
       <c r="J40" s="13">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>670</v>
       </c>
       <c r="K40" s="14" t="s">
         <v>53</v>
@@ -3083,26 +3086,50 @@
       </c>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="11"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="13" t="str">
+      <c r="A41" s="11">
+        <v>46275</v>
+      </c>
+      <c r="B41" s="12">
+        <v>360</v>
+      </c>
+      <c r="C41" s="12">
+        <v>100</v>
+      </c>
+      <c r="D41" s="12">
+        <v>100</v>
+      </c>
+      <c r="E41" s="12">
+        <v>20</v>
+      </c>
+      <c r="F41" s="12">
+        <v>350</v>
+      </c>
+      <c r="G41" s="12">
+        <v>7</v>
+      </c>
+      <c r="H41" s="12">
+        <v>100</v>
+      </c>
+      <c r="I41" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="13" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J41" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="15"/>
+        <v>410</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M41" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="15" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>Had a Headache</t>
+  </si>
+  <si>
+    <t>Celebrated Birthday</t>
   </si>
 </sst>
 </file>
@@ -3132,26 +3135,50 @@
       </c>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="11"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="13" t="str">
+      <c r="A42" s="11">
+        <v>46276</v>
+      </c>
+      <c r="B42" s="12">
+        <v>300</v>
+      </c>
+      <c r="C42" s="12">
+        <v>120</v>
+      </c>
+      <c r="D42" s="12">
+        <v>20</v>
+      </c>
+      <c r="E42" s="12">
+        <v>60</v>
+      </c>
+      <c r="F42" s="12">
+        <v>300</v>
+      </c>
+      <c r="G42" s="12">
+        <v>6</v>
+      </c>
+      <c r="H42" s="12">
+        <v>120</v>
+      </c>
+      <c r="I42" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="13" t="str">
+        <v>920</v>
+      </c>
+      <c r="J42" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="15"/>
+        <v>520</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L42" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M42" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N42" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>Celebrated Birthday</t>
+  </si>
+  <si>
+    <t>Practiced python</t>
   </si>
 </sst>
 </file>
@@ -3181,26 +3184,50 @@
       </c>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="11"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="13" t="str">
+      <c r="A43" s="11">
+        <v>46277</v>
+      </c>
+      <c r="B43" s="12">
+        <v>360</v>
+      </c>
+      <c r="C43" s="12">
+        <v>25</v>
+      </c>
+      <c r="D43" s="12">
+        <v>200</v>
+      </c>
+      <c r="E43" s="12">
+        <v>60</v>
+      </c>
+      <c r="F43" s="12">
+        <v>0</v>
+      </c>
+      <c r="G43" s="12">
+        <v>0</v>
+      </c>
+      <c r="H43" s="12">
+        <v>300</v>
+      </c>
+      <c r="I43" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="13" t="str">
+        <v>945</v>
+      </c>
+      <c r="J43" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="14"/>
-      <c r="N43" s="15"/>
+        <v>495</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M43" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N43" s="15" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>Practiced python</t>
+  </si>
+  <si>
+    <t>Studied SQL</t>
   </si>
 </sst>
 </file>
@@ -3230,26 +3233,50 @@
       </c>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="11"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="13" t="str">
+      <c r="A44" s="11">
+        <v>46278</v>
+      </c>
+      <c r="B44" s="12">
+        <v>400</v>
+      </c>
+      <c r="C44" s="12">
+        <v>30</v>
+      </c>
+      <c r="D44" s="12">
+        <v>120</v>
+      </c>
+      <c r="E44" s="12">
+        <v>150</v>
+      </c>
+      <c r="F44" s="12">
+        <v>0</v>
+      </c>
+      <c r="G44" s="12">
+        <v>0</v>
+      </c>
+      <c r="H44" s="12">
+        <v>500</v>
+      </c>
+      <c r="I44" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="13" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J44" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="14"/>
-      <c r="L44" s="14"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="15"/>
+        <v>240</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L44" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M44" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N44" s="15" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Studied SQL</t>
+  </si>
+  <si>
+    <t>Revised Notes</t>
   </si>
 </sst>
 </file>
@@ -3279,26 +3282,50 @@
       </c>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="11"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="13" t="str">
+      <c r="A45" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B45" s="12">
+        <v>390</v>
+      </c>
+      <c r="C45" s="12">
+        <v>70</v>
+      </c>
+      <c r="D45" s="12">
+        <v>120</v>
+      </c>
+      <c r="E45" s="12">
+        <v>200</v>
+      </c>
+      <c r="F45" s="12">
+        <v>200</v>
+      </c>
+      <c r="G45" s="12">
+        <v>4</v>
+      </c>
+      <c r="H45" s="12">
+        <v>200</v>
+      </c>
+      <c r="I45" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="13" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J45" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="14"/>
-      <c r="L45" s="14"/>
-      <c r="M45" s="14"/>
-      <c r="N45" s="15"/>
+        <v>260</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L45" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M45" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N45" s="15" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6310" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7510" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3328,26 +3328,50 @@
       </c>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="11"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="13" t="str">
+      <c r="A46" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B46" s="12">
+        <v>400</v>
+      </c>
+      <c r="C46" s="12">
+        <v>110</v>
+      </c>
+      <c r="D46" s="12">
+        <v>140</v>
+      </c>
+      <c r="E46" s="12">
+        <v>30</v>
+      </c>
+      <c r="F46" s="12">
+        <v>200</v>
+      </c>
+      <c r="G46" s="12">
+        <v>4</v>
+      </c>
+      <c r="H46" s="12">
+        <v>300</v>
+      </c>
+      <c r="I46" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="13" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J46" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
-      <c r="N46" s="15"/>
+        <v>260</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L46" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M46" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N46" s="15" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7510" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6310" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1575,7 +1575,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N392"/>
   <sheetFormatPr defaultColWidth="8.63636363636364" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1729,11 +1729,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="8">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f>IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="8">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f>IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="9" t="s">
@@ -1750,235 +1750,451 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="13" t="str">
+      <c r="A7" s="11">
+        <v>46250</v>
+      </c>
+      <c r="B7" s="12">
+        <v>420</v>
+      </c>
+      <c r="C7" s="12">
+        <v>39</v>
+      </c>
+      <c r="D7" s="12">
+        <v>90</v>
+      </c>
+      <c r="E7" s="12">
+        <v>20</v>
+      </c>
+      <c r="F7" s="12">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12">
+        <v>40</v>
+      </c>
+      <c r="I7" s="13">
+        <f t="shared" ref="I7:I60" si="0">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <v>609</v>
+      </c>
+      <c r="J7" s="13">
+        <f t="shared" ref="J7:J60" si="1">IF(I7="","",1440-I7)</f>
+        <v>831</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="11">
+        <v>46251</v>
+      </c>
+      <c r="B8" s="12">
+        <v>510</v>
+      </c>
+      <c r="C8" s="12">
+        <v>45</v>
+      </c>
+      <c r="D8" s="12">
+        <v>60</v>
+      </c>
+      <c r="E8" s="12">
+        <v>60</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12">
+        <v>20</v>
+      </c>
+      <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="13" t="str">
+        <v>695</v>
+      </c>
+      <c r="J8" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="15"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="13" t="str">
+        <v>745</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="11">
+        <v>46252</v>
+      </c>
+      <c r="B9" s="12">
+        <v>390</v>
+      </c>
+      <c r="C9" s="12">
+        <v>20</v>
+      </c>
+      <c r="D9" s="12">
+        <v>30</v>
+      </c>
+      <c r="E9" s="12">
+        <v>20</v>
+      </c>
+      <c r="F9" s="12">
+        <v>350</v>
+      </c>
+      <c r="G9" s="12">
+        <v>7</v>
+      </c>
+      <c r="H9" s="12">
+        <v>10</v>
+      </c>
+      <c r="I9" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="13" t="str">
+        <v>820</v>
+      </c>
+      <c r="J9" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="15"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="13" t="str">
+        <v>620</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="11">
+        <v>46253</v>
+      </c>
+      <c r="B10" s="12">
+        <v>400</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12">
+        <v>60</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
+        <v>300</v>
+      </c>
+      <c r="G10" s="12">
+        <v>6</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="13" t="str">
+        <v>760</v>
+      </c>
+      <c r="J10" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="15"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="13" t="str">
+        <v>680</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="11">
+        <v>46254</v>
+      </c>
+      <c r="B11" s="12">
+        <v>360</v>
+      </c>
+      <c r="C11" s="12">
+        <v>12</v>
+      </c>
+      <c r="D11" s="12">
+        <v>40</v>
+      </c>
+      <c r="E11" s="12">
+        <v>20</v>
+      </c>
+      <c r="F11" s="12">
+        <v>410</v>
+      </c>
+      <c r="G11" s="12">
+        <v>8</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0</v>
+      </c>
+      <c r="I11" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="13" t="str">
+        <v>842</v>
+      </c>
+      <c r="J11" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="15"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="13" t="str">
+        <v>598</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="11">
+        <v>46255</v>
+      </c>
+      <c r="B12" s="12">
+        <v>370</v>
+      </c>
+      <c r="C12" s="12">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12">
+        <v>50</v>
+      </c>
+      <c r="F12" s="12">
+        <v>300</v>
+      </c>
+      <c r="G12" s="12">
+        <v>6</v>
+      </c>
+      <c r="H12" s="12">
+        <v>15</v>
+      </c>
+      <c r="I12" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="13" t="str">
+        <v>735</v>
+      </c>
+      <c r="J12" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="15"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="13" t="str">
+        <v>705</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="11">
+        <v>46256</v>
+      </c>
+      <c r="B13" s="12">
+        <v>450</v>
+      </c>
+      <c r="C13" s="12">
+        <v>5</v>
+      </c>
+      <c r="D13" s="12">
+        <v>60</v>
+      </c>
+      <c r="E13" s="12">
+        <v>10</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12">
+        <v>20</v>
+      </c>
+      <c r="I13" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="13" t="str">
+        <v>545</v>
+      </c>
+      <c r="J13" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="15"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="13" t="str">
+        <v>895</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="11">
+        <v>46257</v>
+      </c>
+      <c r="B14" s="12">
+        <v>350</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0</v>
+      </c>
+      <c r="D14" s="12">
+        <v>120</v>
+      </c>
+      <c r="E14" s="12">
+        <v>30</v>
+      </c>
+      <c r="F14" s="12">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12">
+        <v>10</v>
+      </c>
+      <c r="I14" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="13" t="str">
+        <v>510</v>
+      </c>
+      <c r="J14" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="15"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="13" t="str">
+        <v>930</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="11">
+        <v>46258</v>
+      </c>
+      <c r="B15" s="12">
+        <v>374</v>
+      </c>
+      <c r="C15" s="12">
+        <v>12</v>
+      </c>
+      <c r="D15" s="12">
+        <v>60</v>
+      </c>
+      <c r="E15" s="12">
+        <v>10</v>
+      </c>
+      <c r="F15" s="12">
+        <v>200</v>
+      </c>
+      <c r="G15" s="12">
+        <v>4</v>
+      </c>
+      <c r="H15" s="12">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="13" t="str">
+        <v>656</v>
+      </c>
+      <c r="J15" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="15"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="15"/>
+        <v>784</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="11">
-        <v>46250</v>
+        <v>46259</v>
       </c>
       <c r="B16" s="12">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C16" s="12">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D16" s="12">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E16" s="12">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F16" s="12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G16" s="12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" s="12">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I16" s="13">
         <f t="shared" si="0"/>
-        <v>609</v>
+        <v>810</v>
       </c>
       <c r="J16" s="13">
         <f t="shared" si="1"/>
-        <v>831</v>
+        <v>630</v>
       </c>
       <c r="K16" s="14" t="s">
         <v>53</v>
@@ -1987,44 +2203,44 @@
         <v>54</v>
       </c>
       <c r="M16" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N16" s="15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="11">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="B17" s="12">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="C17" s="12">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D17" s="12">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E17" s="12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F17" s="12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G17" s="12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17" s="12">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I17" s="13">
         <f t="shared" si="0"/>
-        <v>695</v>
+        <v>790</v>
       </c>
       <c r="J17" s="13">
         <f t="shared" si="1"/>
-        <v>745</v>
+        <v>650</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>53</v>
@@ -2033,185 +2249,185 @@
         <v>54</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="11">
-        <v>46252</v>
+        <v>46261</v>
       </c>
       <c r="B18" s="12">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="C18" s="12">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D18" s="12">
+        <v>50</v>
+      </c>
+      <c r="E18" s="12">
         <v>30</v>
       </c>
-      <c r="E18" s="12">
-        <v>20</v>
-      </c>
       <c r="F18" s="12">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G18" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I18" s="13">
         <f t="shared" si="0"/>
-        <v>820</v>
+        <v>850</v>
       </c>
       <c r="J18" s="13">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>590</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="L18" s="14" t="s">
         <v>54</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N18" s="15" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="11">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B19" s="12">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C19" s="12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D19" s="12">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E19" s="12">
         <v>0</v>
       </c>
       <c r="F19" s="12">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G19" s="12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H19" s="12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I19" s="13">
         <f t="shared" si="0"/>
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="J19" s="13">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>520</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N19" s="15" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="11">
-        <v>46254</v>
+        <v>46263</v>
       </c>
       <c r="B20" s="12">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="C20" s="12">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D20" s="12">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E20" s="12">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F20" s="12">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="G20" s="12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H20" s="12">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I20" s="13">
         <f t="shared" si="0"/>
-        <v>842</v>
+        <v>780</v>
       </c>
       <c r="J20" s="13">
         <f t="shared" si="1"/>
-        <v>598</v>
+        <v>660</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N20" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="11">
-        <v>46255</v>
+        <v>46264</v>
       </c>
       <c r="B21" s="12">
-        <v>370</v>
+        <v>480</v>
       </c>
       <c r="C21" s="12">
+        <v>60</v>
+      </c>
+      <c r="D21" s="12">
+        <v>120</v>
+      </c>
+      <c r="E21" s="12">
+        <v>100</v>
+      </c>
+      <c r="F21" s="12">
         <v>0</v>
       </c>
-      <c r="D21" s="12">
+      <c r="G21" s="12">
         <v>0</v>
       </c>
-      <c r="E21" s="12">
+      <c r="H21" s="12">
         <v>50</v>
-      </c>
-      <c r="F21" s="12">
-        <v>300</v>
-      </c>
-      <c r="G21" s="12">
-        <v>6</v>
-      </c>
-      <c r="H21" s="12">
-        <v>15</v>
       </c>
       <c r="I21" s="13">
         <f t="shared" si="0"/>
-        <v>735</v>
+        <v>810</v>
       </c>
       <c r="J21" s="13">
         <f t="shared" si="1"/>
-        <v>705</v>
+        <v>630</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L21" s="14" t="s">
         <v>54</v>
@@ -2220,87 +2436,87 @@
         <v>55</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="11">
-        <v>46256</v>
+        <v>46265</v>
       </c>
       <c r="B22" s="12">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C22" s="12">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D22" s="12">
         <v>60</v>
       </c>
       <c r="E22" s="12">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F22" s="12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" s="12">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="I22" s="13">
         <f t="shared" si="0"/>
-        <v>545</v>
+        <v>760</v>
       </c>
       <c r="J22" s="13">
         <f t="shared" si="1"/>
-        <v>895</v>
+        <v>680</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="M22" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N22" s="15" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="11">
-        <v>46257</v>
+        <v>46266</v>
       </c>
       <c r="B23" s="12">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="C23" s="12">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D23" s="12">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E23" s="12">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F23" s="12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G23" s="12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H23" s="12">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="I23" s="13">
         <f t="shared" si="0"/>
-        <v>510</v>
+        <v>1090</v>
       </c>
       <c r="J23" s="13">
         <f t="shared" si="1"/>
-        <v>930</v>
+        <v>350</v>
       </c>
       <c r="K23" s="14" t="s">
         <v>53</v>
@@ -2312,41 +2528,41 @@
         <v>55</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="11">
-        <v>46258</v>
+        <v>46267</v>
       </c>
       <c r="B24" s="12">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="C24" s="12">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D24" s="12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E24" s="12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F24" s="12">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G24" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H24" s="12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24" s="13">
         <f t="shared" si="0"/>
-        <v>656</v>
+        <v>860</v>
       </c>
       <c r="J24" s="13">
         <f t="shared" si="1"/>
-        <v>784</v>
+        <v>580</v>
       </c>
       <c r="K24" s="14" t="s">
         <v>67</v>
@@ -2358,41 +2574,41 @@
         <v>57</v>
       </c>
       <c r="N24" s="15" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="11">
-        <v>46259</v>
+        <v>46268</v>
       </c>
       <c r="B25" s="12">
         <v>400</v>
       </c>
       <c r="C25" s="12">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D25" s="12">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E25" s="12">
         <v>60</v>
       </c>
       <c r="F25" s="12">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G25" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" s="12">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I25" s="13">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>1085</v>
       </c>
       <c r="J25" s="13">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>355</v>
       </c>
       <c r="K25" s="14" t="s">
         <v>53</v>
@@ -2404,90 +2620,90 @@
         <v>55</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="11">
-        <v>46260</v>
+        <v>46269</v>
       </c>
       <c r="B26" s="12">
+        <v>350</v>
+      </c>
+      <c r="C26" s="12">
+        <v>20</v>
+      </c>
+      <c r="D26" s="12">
+        <v>200</v>
+      </c>
+      <c r="E26" s="12">
+        <v>20</v>
+      </c>
+      <c r="F26" s="12">
         <v>300</v>
       </c>
-      <c r="C26" s="12">
-        <v>50</v>
-      </c>
-      <c r="D26" s="12">
-        <v>100</v>
-      </c>
-      <c r="E26" s="12">
-        <v>50</v>
-      </c>
-      <c r="F26" s="12">
-        <v>250</v>
-      </c>
       <c r="G26" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H26" s="12">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I26" s="13">
         <f t="shared" si="0"/>
-        <v>790</v>
+        <v>970</v>
       </c>
       <c r="J26" s="13">
         <f t="shared" si="1"/>
-        <v>650</v>
+        <v>470</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L26" s="14" t="s">
         <v>54</v>
       </c>
       <c r="M26" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N26" s="15" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="11">
-        <v>46261</v>
+        <v>46270</v>
       </c>
       <c r="B27" s="12">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="C27" s="12">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D27" s="12">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="E27" s="12">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="F27" s="12">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G27" s="12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H27" s="12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="13">
         <f t="shared" si="0"/>
-        <v>850</v>
+        <v>668</v>
       </c>
       <c r="J27" s="13">
         <f t="shared" si="1"/>
-        <v>590</v>
+        <v>772</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L27" s="14" t="s">
         <v>54</v>
@@ -2496,133 +2712,133 @@
         <v>57</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="11">
-        <v>46262</v>
+        <v>46271</v>
       </c>
       <c r="B28" s="12">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C28" s="12">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D28" s="12">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="E28" s="12">
+        <v>60</v>
+      </c>
+      <c r="F28" s="12">
         <v>0</v>
       </c>
-      <c r="F28" s="12">
-        <v>200</v>
-      </c>
       <c r="G28" s="12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H28" s="12">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="I28" s="13">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>690</v>
       </c>
       <c r="J28" s="13">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>750</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="M28" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N28" s="15" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="11">
-        <v>46263</v>
+        <v>46272</v>
       </c>
       <c r="B29" s="12">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C29" s="12">
+        <v>40</v>
+      </c>
+      <c r="D29" s="12">
         <v>50</v>
       </c>
-      <c r="D29" s="12">
-        <v>70</v>
-      </c>
       <c r="E29" s="12">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F29" s="12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G29" s="12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H29" s="12">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="I29" s="13">
         <f t="shared" si="0"/>
-        <v>780</v>
+        <v>970</v>
       </c>
       <c r="J29" s="13">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>470</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="M29" s="14" t="s">
         <v>55</v>
       </c>
       <c r="N29" s="15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="11">
-        <v>46264</v>
+        <v>46273</v>
       </c>
       <c r="B30" s="12">
-        <v>480</v>
+        <v>350</v>
       </c>
       <c r="C30" s="12">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D30" s="12">
+        <v>100</v>
+      </c>
+      <c r="E30" s="12">
+        <v>70</v>
+      </c>
+      <c r="F30" s="12">
+        <v>250</v>
+      </c>
+      <c r="G30" s="12">
+        <v>5</v>
+      </c>
+      <c r="H30" s="12">
         <v>120</v>
-      </c>
-      <c r="E30" s="12">
-        <v>100</v>
-      </c>
-      <c r="F30" s="12">
-        <v>0</v>
-      </c>
-      <c r="G30" s="12">
-        <v>0</v>
-      </c>
-      <c r="H30" s="12">
-        <v>50</v>
       </c>
       <c r="I30" s="13">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>930</v>
       </c>
       <c r="J30" s="13">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>510</v>
       </c>
       <c r="K30" s="14" t="s">
         <v>53</v>
@@ -2634,24 +2850,24 @@
         <v>55</v>
       </c>
       <c r="N30" s="15" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="11">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="B31" s="12">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="C31" s="12">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D31" s="12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E31" s="12">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F31" s="12">
         <v>100</v>
@@ -2660,61 +2876,61 @@
         <v>2</v>
       </c>
       <c r="H31" s="12">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="I31" s="13">
         <f t="shared" si="0"/>
-        <v>760</v>
+        <v>770</v>
       </c>
       <c r="J31" s="13">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="K31" s="14" t="s">
         <v>53</v>
       </c>
       <c r="L31" s="14" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="M31" s="14" t="s">
         <v>55</v>
       </c>
       <c r="N31" s="15" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="11">
-        <v>46266</v>
+        <v>46275</v>
       </c>
       <c r="B32" s="12">
-        <v>410</v>
+        <v>360</v>
       </c>
       <c r="C32" s="12">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D32" s="12">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E32" s="12">
+        <v>20</v>
+      </c>
+      <c r="F32" s="12">
+        <v>350</v>
+      </c>
+      <c r="G32" s="12">
+        <v>7</v>
+      </c>
+      <c r="H32" s="12">
         <v>100</v>
-      </c>
-      <c r="F32" s="12">
-        <v>250</v>
-      </c>
-      <c r="G32" s="12">
-        <v>5</v>
-      </c>
-      <c r="H32" s="12">
-        <v>70</v>
       </c>
       <c r="I32" s="13">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1030</v>
       </c>
       <c r="J32" s="13">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="K32" s="14" t="s">
         <v>53</v>
@@ -2726,44 +2942,44 @@
         <v>55</v>
       </c>
       <c r="N32" s="15" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="11">
-        <v>46267</v>
+        <v>46276</v>
       </c>
       <c r="B33" s="12">
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="C33" s="12">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="D33" s="12">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E33" s="12">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F33" s="12">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G33" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H33" s="12">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I33" s="13">
         <f t="shared" si="0"/>
-        <v>860</v>
+        <v>920</v>
       </c>
       <c r="J33" s="13">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>520</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="L33" s="14" t="s">
         <v>70</v>
@@ -2772,41 +2988,41 @@
         <v>57</v>
       </c>
       <c r="N33" s="15" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="11">
-        <v>46268</v>
+        <v>46277</v>
       </c>
       <c r="B34" s="12">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="C34" s="12">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D34" s="12">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E34" s="12">
         <v>60</v>
       </c>
       <c r="F34" s="12">
+        <v>0</v>
+      </c>
+      <c r="G34" s="12">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12">
         <v>300</v>
-      </c>
-      <c r="G34" s="12">
-        <v>6</v>
-      </c>
-      <c r="H34" s="12">
-        <v>45</v>
       </c>
       <c r="I34" s="13">
         <f t="shared" si="0"/>
-        <v>1085</v>
+        <v>945</v>
       </c>
       <c r="J34" s="13">
         <f t="shared" si="1"/>
-        <v>355</v>
+        <v>495</v>
       </c>
       <c r="K34" s="14" t="s">
         <v>53</v>
@@ -2818,90 +3034,90 @@
         <v>55</v>
       </c>
       <c r="N34" s="15" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="11">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B35" s="12">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="C35" s="12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D35" s="12">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E35" s="12">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="F35" s="12">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G35" s="12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H35" s="12">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="I35" s="13">
         <f t="shared" si="0"/>
-        <v>970</v>
+        <v>1200</v>
       </c>
       <c r="J35" s="13">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>240</v>
       </c>
       <c r="K35" s="14" t="s">
         <v>62</v>
       </c>
       <c r="L35" s="14" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="M35" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N35" s="15" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="11">
-        <v>46270</v>
+        <v>46279</v>
       </c>
       <c r="B36" s="12">
-        <v>320</v>
+        <v>390</v>
       </c>
       <c r="C36" s="12">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D36" s="12">
         <v>120</v>
       </c>
       <c r="E36" s="12">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="F36" s="12">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G36" s="12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H36" s="12">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I36" s="13">
         <f t="shared" si="0"/>
-        <v>668</v>
+        <v>1180</v>
       </c>
       <c r="J36" s="13">
         <f t="shared" si="1"/>
-        <v>772</v>
+        <v>260</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="L36" s="14" t="s">
         <v>54</v>
@@ -2910,50 +3126,50 @@
         <v>57</v>
       </c>
       <c r="N36" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="11">
-        <v>46271</v>
+        <v>46280</v>
       </c>
       <c r="B37" s="12">
         <v>400</v>
       </c>
       <c r="C37" s="12">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D37" s="12">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E37" s="12">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F37" s="12">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G37" s="12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H37" s="12">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="I37" s="13">
         <f t="shared" si="0"/>
-        <v>690</v>
+        <v>1180</v>
       </c>
       <c r="J37" s="13">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>260</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L37" s="14" t="s">
         <v>54</v>
       </c>
       <c r="M37" s="14" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N37" s="15" t="s">
         <v>82</v>
@@ -2961,19 +3177,19 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="11">
-        <v>46272</v>
+        <v>46281</v>
       </c>
       <c r="B38" s="12">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="C38" s="12">
         <v>40</v>
       </c>
       <c r="D38" s="12">
+        <v>120</v>
+      </c>
+      <c r="E38" s="12">
         <v>50</v>
-      </c>
-      <c r="E38" s="12">
-        <v>30</v>
       </c>
       <c r="F38" s="12">
         <v>250</v>
@@ -2986,392 +3202,200 @@
       </c>
       <c r="I38" s="13">
         <f t="shared" si="0"/>
-        <v>970</v>
+        <v>1010</v>
       </c>
       <c r="J38" s="13">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L38" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M38" s="14" t="s">
         <v>55</v>
       </c>
       <c r="N38" s="15" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="11">
-        <v>46273</v>
-      </c>
-      <c r="B39" s="12">
-        <v>350</v>
-      </c>
-      <c r="C39" s="12">
-        <v>40</v>
-      </c>
-      <c r="D39" s="12">
-        <v>100</v>
-      </c>
-      <c r="E39" s="12">
-        <v>70</v>
-      </c>
-      <c r="F39" s="12">
-        <v>250</v>
-      </c>
-      <c r="G39" s="12">
-        <v>5</v>
-      </c>
-      <c r="H39" s="12">
-        <v>120</v>
-      </c>
-      <c r="I39" s="13">
+      <c r="A39" s="11"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>930</v>
-      </c>
-      <c r="J39" s="13">
+        <v/>
+      </c>
+      <c r="J39" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>510</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="L39" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M39" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="N39" s="15" t="s">
-        <v>82</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="15"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="11">
-        <v>46274</v>
-      </c>
-      <c r="B40" s="12">
-        <v>340</v>
-      </c>
-      <c r="C40" s="12">
-        <v>20</v>
-      </c>
-      <c r="D40" s="12">
-        <v>50</v>
-      </c>
-      <c r="E40" s="12">
-        <v>120</v>
-      </c>
-      <c r="F40" s="12">
-        <v>100</v>
-      </c>
-      <c r="G40" s="12">
-        <v>2</v>
-      </c>
-      <c r="H40" s="12">
-        <v>140</v>
-      </c>
-      <c r="I40" s="13">
+      <c r="A40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>770</v>
-      </c>
-      <c r="J40" s="13">
+        <v/>
+      </c>
+      <c r="J40" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>670</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="L40" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M40" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="N40" s="15" t="s">
-        <v>83</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="15"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="11">
-        <v>46275</v>
-      </c>
-      <c r="B41" s="12">
-        <v>360</v>
-      </c>
-      <c r="C41" s="12">
-        <v>100</v>
-      </c>
-      <c r="D41" s="12">
-        <v>100</v>
-      </c>
-      <c r="E41" s="12">
-        <v>20</v>
-      </c>
-      <c r="F41" s="12">
-        <v>350</v>
-      </c>
-      <c r="G41" s="12">
-        <v>7</v>
-      </c>
-      <c r="H41" s="12">
-        <v>100</v>
-      </c>
-      <c r="I41" s="13">
+      <c r="A41" s="11"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>1030</v>
-      </c>
-      <c r="J41" s="13">
+        <v/>
+      </c>
+      <c r="J41" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>410</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="L41" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M41" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="N41" s="15" t="s">
-        <v>84</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="15"/>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="11">
-        <v>46276</v>
-      </c>
-      <c r="B42" s="12">
-        <v>300</v>
-      </c>
-      <c r="C42" s="12">
-        <v>120</v>
-      </c>
-      <c r="D42" s="12">
-        <v>20</v>
-      </c>
-      <c r="E42" s="12">
-        <v>60</v>
-      </c>
-      <c r="F42" s="12">
-        <v>300</v>
-      </c>
-      <c r="G42" s="12">
-        <v>6</v>
-      </c>
-      <c r="H42" s="12">
-        <v>120</v>
-      </c>
-      <c r="I42" s="13">
+      <c r="A42" s="11"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>920</v>
-      </c>
-      <c r="J42" s="13">
+        <v/>
+      </c>
+      <c r="J42" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>520</v>
-      </c>
-      <c r="K42" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="L42" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="M42" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="N42" s="15" t="s">
-        <v>85</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="15"/>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="11">
-        <v>46277</v>
-      </c>
-      <c r="B43" s="12">
-        <v>360</v>
-      </c>
-      <c r="C43" s="12">
-        <v>25</v>
-      </c>
-      <c r="D43" s="12">
-        <v>200</v>
-      </c>
-      <c r="E43" s="12">
-        <v>60</v>
-      </c>
-      <c r="F43" s="12">
-        <v>0</v>
-      </c>
-      <c r="G43" s="12">
-        <v>0</v>
-      </c>
-      <c r="H43" s="12">
-        <v>300</v>
-      </c>
-      <c r="I43" s="13">
+      <c r="A43" s="11"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>945</v>
-      </c>
-      <c r="J43" s="13">
+        <v/>
+      </c>
+      <c r="J43" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>495</v>
-      </c>
-      <c r="K43" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="L43" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M43" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="N43" s="15" t="s">
-        <v>86</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="15"/>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="11">
-        <v>46278</v>
-      </c>
-      <c r="B44" s="12">
-        <v>400</v>
-      </c>
-      <c r="C44" s="12">
-        <v>30</v>
-      </c>
-      <c r="D44" s="12">
-        <v>120</v>
-      </c>
-      <c r="E44" s="12">
-        <v>150</v>
-      </c>
-      <c r="F44" s="12">
-        <v>0</v>
-      </c>
-      <c r="G44" s="12">
-        <v>0</v>
-      </c>
-      <c r="H44" s="12">
-        <v>500</v>
-      </c>
-      <c r="I44" s="13">
+      <c r="A44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>1200</v>
-      </c>
-      <c r="J44" s="13">
+        <v/>
+      </c>
+      <c r="J44" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>240</v>
-      </c>
-      <c r="K44" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="L44" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="M44" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="N44" s="15" t="s">
-        <v>87</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="15"/>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="11">
-        <v>46279</v>
-      </c>
-      <c r="B45" s="12">
-        <v>390</v>
-      </c>
-      <c r="C45" s="12">
-        <v>70</v>
-      </c>
-      <c r="D45" s="12">
-        <v>120</v>
-      </c>
-      <c r="E45" s="12">
-        <v>200</v>
-      </c>
-      <c r="F45" s="12">
-        <v>200</v>
-      </c>
-      <c r="G45" s="12">
-        <v>4</v>
-      </c>
-      <c r="H45" s="12">
-        <v>200</v>
-      </c>
-      <c r="I45" s="13">
+      <c r="A45" s="11"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>1180</v>
-      </c>
-      <c r="J45" s="13">
+        <v/>
+      </c>
+      <c r="J45" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>260</v>
-      </c>
-      <c r="K45" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="L45" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M45" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="N45" s="15" t="s">
-        <v>88</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K45" s="14"/>
+      <c r="L45" s="14"/>
+      <c r="M45" s="14"/>
+      <c r="N45" s="15"/>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="11">
-        <v>46280</v>
-      </c>
-      <c r="B46" s="12">
-        <v>400</v>
-      </c>
-      <c r="C46" s="12">
-        <v>110</v>
-      </c>
-      <c r="D46" s="12">
-        <v>140</v>
-      </c>
-      <c r="E46" s="12">
-        <v>30</v>
-      </c>
-      <c r="F46" s="12">
-        <v>200</v>
-      </c>
-      <c r="G46" s="12">
-        <v>4</v>
-      </c>
-      <c r="H46" s="12">
-        <v>300</v>
-      </c>
-      <c r="I46" s="13">
+      <c r="A46" s="11"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>1180</v>
-      </c>
-      <c r="J46" s="13">
+        <v/>
+      </c>
+      <c r="J46" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>260</v>
-      </c>
-      <c r="K46" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="L46" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M46" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="N46" s="15" t="s">
-        <v>82</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
+      <c r="M46" s="14"/>
+      <c r="N46" s="15"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="11"/>
@@ -3691,11 +3715,11 @@
       <c r="G61" s="12"/>
       <c r="H61" s="12"/>
       <c r="I61" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I61:I124" si="2">IF(SUM(B61:F61,H61)=0,"",SUM(B61:F61,H61))</f>
         <v/>
       </c>
       <c r="J61" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J61:J124" si="3">IF(I61="","",1440-I61)</f>
         <v/>
       </c>
       <c r="K61" s="14"/>
@@ -3713,11 +3737,11 @@
       <c r="G62" s="12"/>
       <c r="H62" s="12"/>
       <c r="I62" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J62" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K62" s="14"/>
@@ -3735,11 +3759,11 @@
       <c r="G63" s="12"/>
       <c r="H63" s="12"/>
       <c r="I63" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J63" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K63" s="14"/>
@@ -3757,11 +3781,11 @@
       <c r="G64" s="12"/>
       <c r="H64" s="12"/>
       <c r="I64" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J64" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K64" s="14"/>
@@ -3779,11 +3803,11 @@
       <c r="G65" s="12"/>
       <c r="H65" s="12"/>
       <c r="I65" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J65" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K65" s="14"/>
@@ -3801,11 +3825,11 @@
       <c r="G66" s="12"/>
       <c r="H66" s="12"/>
       <c r="I66" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J66" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K66" s="14"/>
@@ -3823,11 +3847,11 @@
       <c r="G67" s="12"/>
       <c r="H67" s="12"/>
       <c r="I67" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J67" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K67" s="14"/>
@@ -3845,11 +3869,11 @@
       <c r="G68" s="12"/>
       <c r="H68" s="12"/>
       <c r="I68" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J68" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K68" s="14"/>
@@ -3867,11 +3891,11 @@
       <c r="G69" s="12"/>
       <c r="H69" s="12"/>
       <c r="I69" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J69" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K69" s="14"/>
@@ -3889,11 +3913,11 @@
       <c r="G70" s="12"/>
       <c r="H70" s="12"/>
       <c r="I70" s="13" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J70" s="13" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K70" s="14"/>
@@ -5099,11 +5123,11 @@
       <c r="G125" s="12"/>
       <c r="H125" s="12"/>
       <c r="I125" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I125:I188" si="4">IF(SUM(B125:F125,H125)=0,"",SUM(B125:F125,H125))</f>
         <v/>
       </c>
       <c r="J125" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J125:J188" si="5">IF(I125="","",1440-I125)</f>
         <v/>
       </c>
       <c r="K125" s="14"/>
@@ -5121,11 +5145,11 @@
       <c r="G126" s="12"/>
       <c r="H126" s="12"/>
       <c r="I126" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="14"/>
@@ -5143,11 +5167,11 @@
       <c r="G127" s="12"/>
       <c r="H127" s="12"/>
       <c r="I127" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="14"/>
@@ -5165,11 +5189,11 @@
       <c r="G128" s="12"/>
       <c r="H128" s="12"/>
       <c r="I128" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="14"/>
@@ -5187,11 +5211,11 @@
       <c r="G129" s="12"/>
       <c r="H129" s="12"/>
       <c r="I129" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="14"/>
@@ -5209,11 +5233,11 @@
       <c r="G130" s="12"/>
       <c r="H130" s="12"/>
       <c r="I130" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="14"/>
@@ -5231,11 +5255,11 @@
       <c r="G131" s="12"/>
       <c r="H131" s="12"/>
       <c r="I131" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="14"/>
@@ -5253,11 +5277,11 @@
       <c r="G132" s="12"/>
       <c r="H132" s="12"/>
       <c r="I132" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="14"/>
@@ -5275,11 +5299,11 @@
       <c r="G133" s="12"/>
       <c r="H133" s="12"/>
       <c r="I133" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="14"/>
@@ -5297,11 +5321,11 @@
       <c r="G134" s="12"/>
       <c r="H134" s="12"/>
       <c r="I134" s="13" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J134" s="13" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K134" s="14"/>
@@ -6507,11 +6531,11 @@
       <c r="G189" s="12"/>
       <c r="H189" s="12"/>
       <c r="I189" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I189:I252" si="6">IF(SUM(B189:F189,H189)=0,"",SUM(B189:F189,H189))</f>
         <v/>
       </c>
       <c r="J189" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J189:J252" si="7">IF(I189="","",1440-I189)</f>
         <v/>
       </c>
       <c r="K189" s="14"/>
@@ -6529,11 +6553,11 @@
       <c r="G190" s="12"/>
       <c r="H190" s="12"/>
       <c r="I190" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="14"/>
@@ -6551,11 +6575,11 @@
       <c r="G191" s="12"/>
       <c r="H191" s="12"/>
       <c r="I191" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="14"/>
@@ -6573,11 +6597,11 @@
       <c r="G192" s="12"/>
       <c r="H192" s="12"/>
       <c r="I192" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="14"/>
@@ -6595,11 +6619,11 @@
       <c r="G193" s="12"/>
       <c r="H193" s="12"/>
       <c r="I193" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="14"/>
@@ -6617,11 +6641,11 @@
       <c r="G194" s="12"/>
       <c r="H194" s="12"/>
       <c r="I194" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="14"/>
@@ -6639,11 +6663,11 @@
       <c r="G195" s="12"/>
       <c r="H195" s="12"/>
       <c r="I195" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="14"/>
@@ -6661,11 +6685,11 @@
       <c r="G196" s="12"/>
       <c r="H196" s="12"/>
       <c r="I196" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="14"/>
@@ -6683,11 +6707,11 @@
       <c r="G197" s="12"/>
       <c r="H197" s="12"/>
       <c r="I197" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="14"/>
@@ -6705,11 +6729,11 @@
       <c r="G198" s="12"/>
       <c r="H198" s="12"/>
       <c r="I198" s="13" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J198" s="13" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K198" s="14"/>
@@ -7915,11 +7939,11 @@
       <c r="G253" s="12"/>
       <c r="H253" s="12"/>
       <c r="I253" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I253:I316" si="8">IF(SUM(B253:F253,H253)=0,"",SUM(B253:F253,H253))</f>
         <v/>
       </c>
       <c r="J253" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J253:J316" si="9">IF(I253="","",1440-I253)</f>
         <v/>
       </c>
       <c r="K253" s="14"/>
@@ -7937,11 +7961,11 @@
       <c r="G254" s="12"/>
       <c r="H254" s="12"/>
       <c r="I254" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="14"/>
@@ -7959,11 +7983,11 @@
       <c r="G255" s="12"/>
       <c r="H255" s="12"/>
       <c r="I255" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="14"/>
@@ -7981,11 +8005,11 @@
       <c r="G256" s="12"/>
       <c r="H256" s="12"/>
       <c r="I256" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="14"/>
@@ -8003,11 +8027,11 @@
       <c r="G257" s="12"/>
       <c r="H257" s="12"/>
       <c r="I257" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="14"/>
@@ -8025,11 +8049,11 @@
       <c r="G258" s="12"/>
       <c r="H258" s="12"/>
       <c r="I258" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="14"/>
@@ -8047,11 +8071,11 @@
       <c r="G259" s="12"/>
       <c r="H259" s="12"/>
       <c r="I259" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="14"/>
@@ -8069,11 +8093,11 @@
       <c r="G260" s="12"/>
       <c r="H260" s="12"/>
       <c r="I260" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="14"/>
@@ -8091,11 +8115,11 @@
       <c r="G261" s="12"/>
       <c r="H261" s="12"/>
       <c r="I261" s="13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="14"/>
@@ -8113,11 +8137,11 @@
       <c r="G262" s="12"/>
       <c r="H262" s="12"/>
       <c r="I262" s="13" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J262" s="13" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K262" s="14"/>
@@ -9323,11 +9347,11 @@
       <c r="G317" s="12"/>
       <c r="H317" s="12"/>
       <c r="I317" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I317:I380" si="10">IF(SUM(B317:F317,H317)=0,"",SUM(B317:F317,H317))</f>
         <v/>
       </c>
       <c r="J317" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J317:J380" si="11">IF(I317="","",1440-I317)</f>
         <v/>
       </c>
       <c r="K317" s="14"/>
@@ -9345,11 +9369,11 @@
       <c r="G318" s="12"/>
       <c r="H318" s="12"/>
       <c r="I318" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="14"/>
@@ -9367,11 +9391,11 @@
       <c r="G319" s="12"/>
       <c r="H319" s="12"/>
       <c r="I319" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="14"/>
@@ -9389,11 +9413,11 @@
       <c r="G320" s="12"/>
       <c r="H320" s="12"/>
       <c r="I320" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="14"/>
@@ -9411,11 +9435,11 @@
       <c r="G321" s="12"/>
       <c r="H321" s="12"/>
       <c r="I321" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="14"/>
@@ -9433,11 +9457,11 @@
       <c r="G322" s="12"/>
       <c r="H322" s="12"/>
       <c r="I322" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="14"/>
@@ -9455,11 +9479,11 @@
       <c r="G323" s="12"/>
       <c r="H323" s="12"/>
       <c r="I323" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="14"/>
@@ -9477,11 +9501,11 @@
       <c r="G324" s="12"/>
       <c r="H324" s="12"/>
       <c r="I324" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="14"/>
@@ -9499,11 +9523,11 @@
       <c r="G325" s="12"/>
       <c r="H325" s="12"/>
       <c r="I325" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="14"/>
@@ -9521,11 +9545,11 @@
       <c r="G326" s="12"/>
       <c r="H326" s="12"/>
       <c r="I326" s="13" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J326" s="13" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K326" s="14"/>
@@ -10731,11 +10755,11 @@
       <c r="G381" s="12"/>
       <c r="H381" s="12"/>
       <c r="I381" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I381:I444" si="12">IF(SUM(B381:F381,H381)=0,"",SUM(B381:F381,H381))</f>
         <v/>
       </c>
       <c r="J381" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J381:J444" si="13">IF(I381="","",1440-I381)</f>
         <v/>
       </c>
       <c r="K381" s="14"/>
@@ -10753,11 +10777,11 @@
       <c r="G382" s="12"/>
       <c r="H382" s="12"/>
       <c r="I382" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="14"/>
@@ -10775,11 +10799,11 @@
       <c r="G383" s="12"/>
       <c r="H383" s="12"/>
       <c r="I383" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="14"/>
@@ -10797,11 +10821,11 @@
       <c r="G384" s="12"/>
       <c r="H384" s="12"/>
       <c r="I384" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="14"/>
@@ -10819,11 +10843,11 @@
       <c r="G385" s="12"/>
       <c r="H385" s="12"/>
       <c r="I385" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="14"/>
@@ -10841,11 +10865,11 @@
       <c r="G386" s="12"/>
       <c r="H386" s="12"/>
       <c r="I386" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="14"/>
@@ -10863,11 +10887,11 @@
       <c r="G387" s="12"/>
       <c r="H387" s="12"/>
       <c r="I387" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="14"/>
@@ -10885,11 +10909,11 @@
       <c r="G388" s="12"/>
       <c r="H388" s="12"/>
       <c r="I388" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="14"/>
@@ -10907,11 +10931,11 @@
       <c r="G389" s="12"/>
       <c r="H389" s="12"/>
       <c r="I389" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="14"/>
@@ -10929,11 +10953,11 @@
       <c r="G390" s="12"/>
       <c r="H390" s="12"/>
       <c r="I390" s="13" t="str">
-        <f t="shared" ref="I390:I453" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J390" s="13" t="str">
-        <f t="shared" ref="J390:J453" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K390" s="14"/>
@@ -10985,204 +11009,6 @@
       <c r="M392" s="14"/>
       <c r="N392" s="15"/>
     </row>
-    <row r="393" spans="1:14">
-      <c r="A393" s="11"/>
-      <c r="B393" s="12"/>
-      <c r="C393" s="12"/>
-      <c r="D393" s="12"/>
-      <c r="E393" s="12"/>
-      <c r="F393" s="12"/>
-      <c r="G393" s="12"/>
-      <c r="H393" s="12"/>
-      <c r="I393" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J393" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K393" s="14"/>
-      <c r="L393" s="14"/>
-      <c r="M393" s="14"/>
-      <c r="N393" s="15"/>
-    </row>
-    <row r="394" spans="1:14">
-      <c r="A394" s="11"/>
-      <c r="B394" s="12"/>
-      <c r="C394" s="12"/>
-      <c r="D394" s="12"/>
-      <c r="E394" s="12"/>
-      <c r="F394" s="12"/>
-      <c r="G394" s="12"/>
-      <c r="H394" s="12"/>
-      <c r="I394" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J394" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K394" s="14"/>
-      <c r="L394" s="14"/>
-      <c r="M394" s="14"/>
-      <c r="N394" s="15"/>
-    </row>
-    <row r="395" spans="1:14">
-      <c r="A395" s="11"/>
-      <c r="B395" s="12"/>
-      <c r="C395" s="12"/>
-      <c r="D395" s="12"/>
-      <c r="E395" s="12"/>
-      <c r="F395" s="12"/>
-      <c r="G395" s="12"/>
-      <c r="H395" s="12"/>
-      <c r="I395" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J395" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K395" s="14"/>
-      <c r="L395" s="14"/>
-      <c r="M395" s="14"/>
-      <c r="N395" s="15"/>
-    </row>
-    <row r="396" spans="1:14">
-      <c r="A396" s="11"/>
-      <c r="B396" s="12"/>
-      <c r="C396" s="12"/>
-      <c r="D396" s="12"/>
-      <c r="E396" s="12"/>
-      <c r="F396" s="12"/>
-      <c r="G396" s="12"/>
-      <c r="H396" s="12"/>
-      <c r="I396" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J396" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K396" s="14"/>
-      <c r="L396" s="14"/>
-      <c r="M396" s="14"/>
-      <c r="N396" s="15"/>
-    </row>
-    <row r="397" spans="1:14">
-      <c r="A397" s="11"/>
-      <c r="B397" s="12"/>
-      <c r="C397" s="12"/>
-      <c r="D397" s="12"/>
-      <c r="E397" s="12"/>
-      <c r="F397" s="12"/>
-      <c r="G397" s="12"/>
-      <c r="H397" s="12"/>
-      <c r="I397" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J397" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K397" s="14"/>
-      <c r="L397" s="14"/>
-      <c r="M397" s="14"/>
-      <c r="N397" s="15"/>
-    </row>
-    <row r="398" spans="1:14">
-      <c r="A398" s="11"/>
-      <c r="B398" s="12"/>
-      <c r="C398" s="12"/>
-      <c r="D398" s="12"/>
-      <c r="E398" s="12"/>
-      <c r="F398" s="12"/>
-      <c r="G398" s="12"/>
-      <c r="H398" s="12"/>
-      <c r="I398" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J398" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K398" s="14"/>
-      <c r="L398" s="14"/>
-      <c r="M398" s="14"/>
-      <c r="N398" s="15"/>
-    </row>
-    <row r="399" spans="1:14">
-      <c r="A399" s="11"/>
-      <c r="B399" s="12"/>
-      <c r="C399" s="12"/>
-      <c r="D399" s="12"/>
-      <c r="E399" s="12"/>
-      <c r="F399" s="12"/>
-      <c r="G399" s="12"/>
-      <c r="H399" s="12"/>
-      <c r="I399" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J399" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K399" s="14"/>
-      <c r="L399" s="14"/>
-      <c r="M399" s="14"/>
-      <c r="N399" s="15"/>
-    </row>
-    <row r="400" spans="1:14">
-      <c r="A400" s="11"/>
-      <c r="B400" s="12"/>
-      <c r="C400" s="12"/>
-      <c r="D400" s="12"/>
-      <c r="E400" s="12"/>
-      <c r="F400" s="12"/>
-      <c r="G400" s="12"/>
-      <c r="H400" s="12"/>
-      <c r="I400" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J400" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K400" s="14"/>
-      <c r="L400" s="14"/>
-      <c r="M400" s="14"/>
-      <c r="N400" s="15"/>
-    </row>
-    <row r="401" spans="1:14">
-      <c r="A401" s="11"/>
-      <c r="B401" s="12"/>
-      <c r="C401" s="12"/>
-      <c r="D401" s="12"/>
-      <c r="E401" s="12"/>
-      <c r="F401" s="12"/>
-      <c r="G401" s="12"/>
-      <c r="H401" s="12"/>
-      <c r="I401" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="14"/>
-      <c r="L401" s="14"/>
-      <c r="M401" s="14"/>
-      <c r="N401" s="15"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:N1"/>
@@ -11192,19 +11018,19 @@
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="A4:N4"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J392">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6 K7:K392">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6 L7:L392">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6 M7:M392">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3180,7 +3180,7 @@
         <v>46281</v>
       </c>
       <c r="B38" s="12">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="C38" s="12">
         <v>40</v>
@@ -3202,11 +3202,11 @@
       </c>
       <c r="I38" s="13">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1060</v>
       </c>
       <c r="J38" s="13">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="K38" s="14" t="s">
         <v>62</v>
@@ -3222,26 +3222,50 @@
       </c>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="11"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="13" t="str">
+      <c r="A39" s="11">
+        <v>46282</v>
+      </c>
+      <c r="B39" s="12">
+        <v>350</v>
+      </c>
+      <c r="C39" s="12">
+        <v>60</v>
+      </c>
+      <c r="D39" s="12">
+        <v>60</v>
+      </c>
+      <c r="E39" s="12">
+        <v>60</v>
+      </c>
+      <c r="F39" s="12">
+        <v>250</v>
+      </c>
+      <c r="G39" s="12">
+        <v>5</v>
+      </c>
+      <c r="H39" s="12">
+        <v>200</v>
+      </c>
+      <c r="I39" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="13" t="str">
+        <v>980</v>
+      </c>
+      <c r="J39" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="15"/>
+        <v>460</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N39" s="15" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>Revised Notes</t>
+  </si>
+  <si>
+    <t>solved coding problems</t>
   </si>
 </sst>
 </file>
@@ -3268,70 +3271,142 @@
       </c>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="11"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="13" t="str">
+      <c r="A40" s="11">
+        <v>46283</v>
+      </c>
+      <c r="B40" s="12">
+        <v>420</v>
+      </c>
+      <c r="C40" s="12">
+        <v>50</v>
+      </c>
+      <c r="D40" s="12">
+        <v>140</v>
+      </c>
+      <c r="E40" s="12">
+        <v>60</v>
+      </c>
+      <c r="F40" s="12">
+        <v>300</v>
+      </c>
+      <c r="G40" s="12">
+        <v>6</v>
+      </c>
+      <c r="H40" s="12">
+        <v>300</v>
+      </c>
+      <c r="I40" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="13" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J40" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="15"/>
+        <v>170</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="M40" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N40" s="15" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="11"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="13" t="str">
+      <c r="A41" s="11">
+        <v>46284</v>
+      </c>
+      <c r="B41" s="12">
+        <v>380</v>
+      </c>
+      <c r="C41" s="12">
+        <v>30</v>
+      </c>
+      <c r="D41" s="12">
+        <v>130</v>
+      </c>
+      <c r="E41" s="12">
+        <v>20</v>
+      </c>
+      <c r="F41" s="12">
+        <v>350</v>
+      </c>
+      <c r="G41" s="12">
+        <v>7</v>
+      </c>
+      <c r="H41" s="12">
+        <v>100</v>
+      </c>
+      <c r="I41" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="13" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J41" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="15"/>
+        <v>430</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M41" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="15" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="11"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="13" t="str">
+      <c r="A42" s="11">
+        <v>46285</v>
+      </c>
+      <c r="B42" s="12">
+        <v>400</v>
+      </c>
+      <c r="C42" s="12">
+        <v>20</v>
+      </c>
+      <c r="D42" s="12">
+        <v>120</v>
+      </c>
+      <c r="E42" s="12">
+        <v>30</v>
+      </c>
+      <c r="F42" s="12">
+        <v>0</v>
+      </c>
+      <c r="G42" s="12">
+        <v>0</v>
+      </c>
+      <c r="H42" s="12">
+        <v>400</v>
+      </c>
+      <c r="I42" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="13" t="str">
+        <v>970</v>
+      </c>
+      <c r="J42" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="15"/>
+        <v>470</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L42" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M42" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N42" s="15" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3409,26 +3409,50 @@
       </c>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="11"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="13" t="str">
+      <c r="A43" s="11">
+        <v>46286</v>
+      </c>
+      <c r="B43" s="12">
+        <v>360</v>
+      </c>
+      <c r="C43" s="12">
+        <v>30</v>
+      </c>
+      <c r="D43" s="12">
+        <v>60</v>
+      </c>
+      <c r="E43" s="12">
+        <v>60</v>
+      </c>
+      <c r="F43" s="12">
+        <v>0</v>
+      </c>
+      <c r="G43" s="12">
+        <v>0</v>
+      </c>
+      <c r="H43" s="12">
+        <v>450</v>
+      </c>
+      <c r="I43" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="13" t="str">
+        <v>960</v>
+      </c>
+      <c r="J43" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="14"/>
-      <c r="N43" s="15"/>
+        <v>480</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M43" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N43" s="15" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="11"/>
